--- a/tools/importer/reports/import-eds-page.report.xlsx
+++ b/tools/importer/reports/import-eds-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="104">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,10 +52,10 @@
     <t>eds-page</t>
   </si>
   <si>
-    <t>2026-10-27T11:51:40.372Z</t>
-  </si>
-  <si>
-    <t>Footer Block</t>
+    <t>2026-10-27T17:26:59.087Z</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/footer.plain.html</t>
@@ -70,10 +70,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-10-27T11:51:29.660Z</t>
-  </si>
-  <si>
-    <t>Yippee Noodles &amp; Pasta | Tasty Treats for Every Mood</t>
+    <t>2026-10-27T17:26:50.104Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/index.plain.html</t>
@@ -88,13 +85,244 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-27T11:51:35.166Z</t>
-  </si>
-  <si>
-    <t>Our Story</t>
+    <t>2026-10-27T17:26:54.537Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/nav.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/finger-fries-recipe.report.json</t>
+  </si>
+  <si>
+    <t>["recipe-info"]</t>
+  </si>
+  <si>
+    <t>recipes/finger-fries-recipe</t>
+  </si>
+  <si>
+    <t>recipe</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:35.983Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/finger-fries-recipe.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/masala-noodle-soup.report.json</t>
+  </si>
+  <si>
+    <t>recipes/masala-noodle-soup</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:17.046Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-noodle-soup.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/masala-omelette.report.json</t>
+  </si>
+  <si>
+    <t>recipes/masala-omelette</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:25.040Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-omelette.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-burger.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-burger</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:21.110Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-burger.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-chaat.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-chaat</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:29.879Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-chaat.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-curry.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-curry</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:42.296Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-curry.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-cutlets.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-cutlets</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:52.437Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-cutlets.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-fried-rice.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-fried-rice</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:46.781Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-fried-rice.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-manchurian.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-manchurian</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:01.782Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-manchurian.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-paratha.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-paratha</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:25:58.138Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-paratha.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-pizza.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-pizza</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:05.790Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pizza.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-poha.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-poha</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:10.929Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-poha.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-pulao.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-pulao</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:16.034Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pulao.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-sandwich.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-sandwich</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:21.426Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-sandwich.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-spring-rolls.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-spring-rolls</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:26.783Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-spring-rolls.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-stir-fry.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-stir-fry</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:36.629Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-stir-fry.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-tacos.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-tacos</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:40.905Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-tacos.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodle-upma.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodle-upma</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:45.467Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-upma.plain.html</t>
+  </si>
+  <si>
+    <t>recipes/noodles-chilla.report.json</t>
+  </si>
+  <si>
+    <t>recipes/noodles-chilla</t>
+  </si>
+  <si>
+    <t>2026-10-27T17:26:32.851Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodles-chilla.plain.html</t>
   </si>
 </sst>
 </file>
@@ -483,15 +711,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -566,21 +795,21 @@
         <v>19</v>
       </c>
       <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -589,13 +818,507 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-eds-page.report.xlsx
+++ b/tools/importer/reports/import-eds-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="110">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>eds-page</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:59.087Z</t>
+    <t>2026-10-28T04:28:34.686Z</t>
   </si>
   <si>
     <t/>
@@ -70,7 +70,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:50.104Z</t>
+    <t>2026-10-28T04:28:26.140Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/index.plain.html</t>
@@ -85,12 +85,30 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:54.537Z</t>
+    <t>2026-10-28T04:28:30.505Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/nav.plain.html</t>
   </si>
   <si>
+    <t>pages/index.report.json</t>
+  </si>
+  <si>
+    <t>["sunfeast-yippee-products"]</t>
+  </si>
+  <si>
+    <t>pages/index</t>
+  </si>
+  <si>
+    <t>product-listing</t>
+  </si>
+  <si>
+    <t>2026-10-28T04:22:45.331Z</t>
+  </si>
+  <si>
+    <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/pages/index.plain.html</t>
+  </si>
+  <si>
     <t>recipes/finger-fries-recipe.report.json</t>
   </si>
   <si>
@@ -103,7 +121,7 @@
     <t>recipe</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:35.983Z</t>
+    <t>2026-10-28T04:21:30.468Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/finger-fries-recipe.plain.html</t>
@@ -115,7 +133,7 @@
     <t>recipes/masala-noodle-soup</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:17.046Z</t>
+    <t>2026-10-28T04:21:08.652Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-noodle-soup.plain.html</t>
@@ -127,7 +145,7 @@
     <t>recipes/masala-omelette</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:25.040Z</t>
+    <t>2026-10-28T04:21:20.432Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-omelette.plain.html</t>
@@ -139,7 +157,7 @@
     <t>recipes/noodle-burger</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:21.110Z</t>
+    <t>2026-10-28T04:21:13.666Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-burger.plain.html</t>
@@ -151,7 +169,7 @@
     <t>recipes/noodle-chaat</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:29.879Z</t>
+    <t>2026-10-28T04:21:24.731Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-chaat.plain.html</t>
@@ -163,7 +181,7 @@
     <t>recipes/noodle-curry</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:42.296Z</t>
+    <t>2026-10-28T04:21:35.251Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-curry.plain.html</t>
@@ -175,7 +193,7 @@
     <t>recipes/noodle-cutlets</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:52.437Z</t>
+    <t>2026-10-28T04:21:45.443Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-cutlets.plain.html</t>
@@ -187,7 +205,7 @@
     <t>recipes/noodle-fried-rice</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:46.781Z</t>
+    <t>2026-10-28T04:21:39.849Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-fried-rice.plain.html</t>
@@ -199,7 +217,7 @@
     <t>recipes/noodle-manchurian</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:01.782Z</t>
+    <t>2026-10-28T04:21:54.190Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-manchurian.plain.html</t>
@@ -211,7 +229,7 @@
     <t>recipes/noodle-paratha</t>
   </si>
   <si>
-    <t>2026-10-27T17:25:58.138Z</t>
+    <t>2026-10-28T04:21:49.496Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-paratha.plain.html</t>
@@ -223,7 +241,7 @@
     <t>recipes/noodle-pizza</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:05.790Z</t>
+    <t>2026-10-28T04:21:58.405Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pizza.plain.html</t>
@@ -235,7 +253,7 @@
     <t>recipes/noodle-poha</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:10.929Z</t>
+    <t>2026-10-28T04:22:02.693Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-poha.plain.html</t>
@@ -247,7 +265,7 @@
     <t>recipes/noodle-pulao</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:16.034Z</t>
+    <t>2026-10-28T04:22:08.088Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pulao.plain.html</t>
@@ -259,7 +277,7 @@
     <t>recipes/noodle-sandwich</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:21.426Z</t>
+    <t>2026-10-28T04:22:13.211Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-sandwich.plain.html</t>
@@ -271,7 +289,7 @@
     <t>recipes/noodle-spring-rolls</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:26.783Z</t>
+    <t>2026-10-28T04:22:17.975Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-spring-rolls.plain.html</t>
@@ -283,7 +301,7 @@
     <t>recipes/noodle-stir-fry</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:36.629Z</t>
+    <t>2026-10-28T04:22:27.601Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-stir-fry.plain.html</t>
@@ -295,7 +313,7 @@
     <t>recipes/noodle-tacos</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:40.905Z</t>
+    <t>2026-10-28T04:22:31.467Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-tacos.plain.html</t>
@@ -307,7 +325,7 @@
     <t>recipes/noodle-upma</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:45.467Z</t>
+    <t>2026-10-28T04:22:35.761Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-upma.plain.html</t>
@@ -319,7 +337,7 @@
     <t>recipes/noodles-chilla</t>
   </si>
   <si>
-    <t>2026-10-27T17:26:32.851Z</t>
+    <t>2026-10-28T04:22:22.186Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodles-chilla.plain.html</t>
@@ -711,13 +729,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="7" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
@@ -858,467 +876,493 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
         <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>103</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-eds-page.report.xlsx
+++ b/tools/importer/reports/import-eds-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>eds-page</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:34.686Z</t>
+    <t>2026-10-28T05:01:27.117Z</t>
   </si>
   <si>
     <t/>
@@ -70,7 +70,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:26.140Z</t>
+    <t>2026-10-28T05:01:15.417Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/index.plain.html</t>
@@ -85,7 +85,7 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-28T04:28:30.505Z</t>
+    <t>2026-10-28T05:01:21.051Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/nav.plain.html</t>
@@ -103,7 +103,7 @@
     <t>product-listing</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:45.331Z</t>
+    <t>2026-10-28T04:30:19.469Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/pages/index.plain.html</t>
@@ -121,7 +121,7 @@
     <t>recipe</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:30.468Z</t>
+    <t>2026-10-28T04:29:02.553Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/finger-fries-recipe.plain.html</t>
@@ -133,7 +133,7 @@
     <t>recipes/masala-noodle-soup</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:08.652Z</t>
+    <t>2026-10-28T04:28:43.097Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-noodle-soup.plain.html</t>
@@ -145,7 +145,7 @@
     <t>recipes/masala-omelette</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:20.432Z</t>
+    <t>2026-10-28T04:28:52.245Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/masala-omelette.plain.html</t>
@@ -157,7 +157,7 @@
     <t>recipes/noodle-burger</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:13.666Z</t>
+    <t>2026-10-28T04:28:48.390Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-burger.plain.html</t>
@@ -169,7 +169,7 @@
     <t>recipes/noodle-chaat</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:24.731Z</t>
+    <t>2026-10-28T04:28:57.534Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-chaat.plain.html</t>
@@ -181,7 +181,7 @@
     <t>recipes/noodle-curry</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:35.251Z</t>
+    <t>2026-10-28T04:29:07.000Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-curry.plain.html</t>
@@ -193,7 +193,7 @@
     <t>recipes/noodle-cutlets</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:45.443Z</t>
+    <t>2026-10-28T04:29:17.738Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-cutlets.plain.html</t>
@@ -205,7 +205,7 @@
     <t>recipes/noodle-fried-rice</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:39.849Z</t>
+    <t>2026-10-28T04:29:12.207Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-fried-rice.plain.html</t>
@@ -217,7 +217,7 @@
     <t>recipes/noodle-manchurian</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:54.190Z</t>
+    <t>2026-10-28T04:29:27.445Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-manchurian.plain.html</t>
@@ -229,7 +229,7 @@
     <t>recipes/noodle-paratha</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:49.496Z</t>
+    <t>2026-10-28T04:29:24.121Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-paratha.plain.html</t>
@@ -241,7 +241,7 @@
     <t>recipes/noodle-pizza</t>
   </si>
   <si>
-    <t>2026-10-28T04:21:58.405Z</t>
+    <t>2026-10-28T04:29:32.045Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pizza.plain.html</t>
@@ -253,7 +253,7 @@
     <t>recipes/noodle-poha</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:02.693Z</t>
+    <t>2026-10-28T04:29:36.545Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-poha.plain.html</t>
@@ -265,7 +265,7 @@
     <t>recipes/noodle-pulao</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:08.088Z</t>
+    <t>2026-10-28T04:29:39.937Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-pulao.plain.html</t>
@@ -277,7 +277,7 @@
     <t>recipes/noodle-sandwich</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:13.211Z</t>
+    <t>2026-10-28T04:29:45.186Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-sandwich.plain.html</t>
@@ -289,7 +289,7 @@
     <t>recipes/noodle-spring-rolls</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:17.975Z</t>
+    <t>2026-10-28T04:29:49.345Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-spring-rolls.plain.html</t>
@@ -301,7 +301,7 @@
     <t>recipes/noodle-stir-fry</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:27.601Z</t>
+    <t>2026-10-28T04:29:59.164Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-stir-fry.plain.html</t>
@@ -313,7 +313,7 @@
     <t>recipes/noodle-tacos</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:31.467Z</t>
+    <t>2026-10-28T04:30:04.940Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-tacos.plain.html</t>
@@ -325,7 +325,7 @@
     <t>recipes/noodle-upma</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:35.761Z</t>
+    <t>2026-10-28T04:30:10.802Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodle-upma.plain.html</t>
@@ -337,7 +337,7 @@
     <t>recipes/noodles-chilla</t>
   </si>
   <si>
-    <t>2026-10-28T04:22:22.186Z</t>
+    <t>2026-10-28T04:29:54.672Z</t>
   </si>
   <si>
     <t>https://main--sunfeast-yippee--ankitraj4899.aem.live/recipes/noodles-chilla.plain.html</t>
